--- a/UConnBleedBlue/wwwroot/Data/Costs.xlsx
+++ b/UConnBleedBlue/wwwroot/Data/Costs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Repos\UConnBleedBlue\UConnBleedBlue\wwwroot\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64FD3867-1115-4E15-AFD1-B702FEC8A137}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DB19AA0-C449-41E5-90A1-975C1E1F58A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2670" yWindow="2220" windowWidth="21600" windowHeight="13680" xr2:uid="{CE911E70-E777-478D-A573-EDC5A294280B}"/>
+    <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="13680" xr2:uid="{CE911E70-E777-478D-A573-EDC5A294280B}"/>
   </bookViews>
   <sheets>
     <sheet name="Costs" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>Cost</t>
   </si>
@@ -45,9 +45,6 @@
   </si>
   <si>
     <t>Rent 2 Pickup Trucks</t>
-  </si>
-  <si>
-    <t>Rent 5 Banquet Tables</t>
   </si>
   <si>
     <t>Hamburger, Hotdogs, Sausage, Cheese, Buns</t>
@@ -429,7 +426,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3EE57203-7D3B-4332-A800-641DAE6FF24B}">
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="43.5703125" customWidth="1"/>
@@ -438,14 +435,14 @@
   <sheetData>
     <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D1" s="3">
-        <f>SUM(B2:B16)</f>
-        <v>1644</v>
+        <f>SUM(B2:B15)</f>
+        <v>1574</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -458,18 +455,18 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B3" s="3">
-        <v>70</v>
+        <v>120</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B4" s="3">
-        <v>120</v>
+        <v>900</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -477,7 +474,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="3">
-        <v>900</v>
+        <v>204</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -485,14 +482,6 @@
         <v>5</v>
       </c>
       <c r="B6" s="3">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7" s="3">
         <v>150</v>
       </c>
     </row>

--- a/UConnBleedBlue/wwwroot/Data/Costs.xlsx
+++ b/UConnBleedBlue/wwwroot/Data/Costs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Repos\UConnBleedBlue\UConnBleedBlue\wwwroot\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DB19AA0-C449-41E5-90A1-975C1E1F58A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15961CDF-0CBA-4B25-A845-F7D772B4E35A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="13680" xr2:uid="{CE911E70-E777-478D-A573-EDC5A294280B}"/>
+    <workbookView xWindow="3675" yWindow="1800" windowWidth="21600" windowHeight="13680" xr2:uid="{CE911E70-E777-478D-A573-EDC5A294280B}"/>
   </bookViews>
   <sheets>
     <sheet name="Costs" sheetId="1" r:id="rId1"/>
@@ -41,9 +41,6 @@
     <t>Cost</t>
   </si>
   <si>
-    <t>Ice - 10 35lb Bags</t>
-  </si>
-  <si>
     <t>Rent 2 Pickup Trucks</t>
   </si>
   <si>
@@ -57,6 +54,9 @@
   </si>
   <si>
     <t>Descriptionts</t>
+  </si>
+  <si>
+    <t>Ice - 15 30lb Bags</t>
   </si>
 </sst>
 </file>
@@ -435,7 +435,7 @@
   <sheetData>
     <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>0</v>
@@ -447,7 +447,7 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B2" s="3">
         <v>200</v>
@@ -455,7 +455,7 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B3" s="3">
         <v>120</v>
@@ -463,7 +463,7 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B4" s="3">
         <v>900</v>
@@ -471,7 +471,7 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B5" s="3">
         <v>204</v>
@@ -479,7 +479,7 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B6" s="3">
         <v>150</v>
